--- a/ProjectDescription/VideoInfo_FunctionNameReg.xlsx
+++ b/ProjectDescription/VideoInfo_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1100,6 +1100,622 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>视频信息数据模型，解析yt-dlp返回的JSON数据</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo:19]</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>包含标题、时长、缩略图、格式列表等字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>formatId&lt;String&gt;, ext&lt;String&gt;, resolution&lt;String&gt;, filesize&lt;long&gt;, vcodec&lt;String&gt;, acodec&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>视频格式子类，描述单个可用格式的信息</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo.Format:43]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>含isAudioOnly判断、getFilesizeText大小格式化</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>parseFromJson</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>jsonString&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>从JSON字符串解析为VideoInfo对象</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;parseFromJson:115]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>静态方法，解析失败返回error状态的对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>getDurationText</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>获取格式化的时长文本（X分X秒）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;getDurationText:164]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>将秒数转换为中文时长描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>aggregateByQuality</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>List&lt;Format&gt;</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>按画质聚合格式列表，每种画质只保留一个最佳格式，用于去重显示</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;aggregateByQuality:221]</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>跳过纯音频格式，按360p/720p/1080p分组</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>pickBetterFormat</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>a&lt;Format&gt;, b&lt;Format&gt;</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>比较两个同画质的格式，按非锁定&gt;锁定、合并&gt;纯视频、文件大&gt;文件小的优先级返回更优格式</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;pickBetterFormat:258]</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>静态私有方法，被aggregateByQuality调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>视频信息数据模型，解析yt-dlp返回的JSON数据</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo:19]</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>包含标题、时长、缩略图、格式列表等字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>formatId&lt;String&gt;, ext&lt;String&gt;, resolution&lt;String&gt;, filesize&lt;long&gt;, vcodec&lt;String&gt;, acodec&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>视频格式子类，描述单个可用格式的信息</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo.Format:43]</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>含isAudioOnly判断、getFilesizeText大小格式化</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>parseFromJson</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>jsonString&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>从JSON字符串解析为VideoInfo对象</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;parseFromJson:115]</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>静态方法，解析失败返回error状态的对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>getDurationText</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>获取格式化的时长文本（X分X秒）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;getDurationText:164]</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>将秒数转换为中文时长描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>aggregateByQuality</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>List&lt;Format&gt;</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>按画质聚合格式列表，每种画质只保留一个最佳格式，用于去重显示</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;aggregateByQuality:221]</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>跳过纯音频格式，按360p/720p/1080p分组</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>pickBetterFormat</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>a&lt;Format&gt;, b&lt;Format&gt;</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>比较两个同画质的格式，按非锁定&gt;锁定、合并&gt;纯视频、文件大&gt;文件小的优先级返回更优格式</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;pickBetterFormat:258]</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>静态私有方法，被aggregateByQuality调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>视频信息数据模型，解析yt-dlp返回的JSON数据</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo:19]</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>包含标题、时长、缩略图、格式列表等字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>formatId&lt;String&gt;, ext&lt;String&gt;, resolution&lt;String&gt;, filesize&lt;long&gt;, vcodec&lt;String&gt;, acodec&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>视频格式子类，描述单个可用格式的信息</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo.Format:43]</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>含isAudioOnly判断、getFilesizeText大小格式化</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>parseFromJson</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>jsonString&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>从JSON字符串解析为VideoInfo对象</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;parseFromJson:115]</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>静态方法，解析失败返回error状态的对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>getDurationText</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>获取格式化的时长文本（X分X秒）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;getDurationText:164]</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>将秒数转换为中文时长描述</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/VideoInfo_FunctionNameReg.xlsx
+++ b/ProjectDescription/VideoInfo_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1716,6 +1716,238 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>aggregateByQuality</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>List&lt;Format&gt;</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>按画质聚合格式列表，每种画质只保留一个最佳格式，用于去重显示</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;aggregateByQuality:221]</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>跳过纯音频格式，按360p/720p/1080p分组</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>pickBetterFormat</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>a&lt;Format&gt;, b&lt;Format&gt;</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>比较两个同画质的格式，按非锁定&gt;锁定、合并&gt;纯视频、文件大&gt;文件小的优先级返回更优格式</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;pickBetterFormat:258]</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>静态私有方法，被aggregateByQuality调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>视频信息数据模型，解析yt-dlp返回的JSON数据</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo:19]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>包含标题、时长、缩略图、格式列表等字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>formatId&lt;String&gt;, ext&lt;String&gt;, resolution&lt;String&gt;, filesize&lt;long&gt;, vcodec&lt;String&gt;, acodec&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>视频格式子类，描述单个可用格式的信息</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo.Format:43]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>含isAudioOnly判断、getFilesizeText大小格式化</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>parseFromJson</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>jsonString&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>VideoInfo</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>从JSON字符串解析为VideoInfo对象</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;parseFromJson:115]</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>静态方法，解析失败返回error状态的对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>getDurationText</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>获取格式化的时长文本（X分X秒）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/VideoInfo.java)[VideoInfo-&gt;getDurationText:164]</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>将秒数转换为中文时长描述</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
